--- a/artfynd/A 28-2025 artfynd.xlsx
+++ b/artfynd/A 28-2025 artfynd.xlsx
@@ -1293,10 +1293,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122309088</v>
+        <v>122310052</v>
       </c>
       <c r="B7" t="n">
-        <v>79263</v>
+        <v>91397</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1305,25 +1305,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1333,10 +1333,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>664875</v>
+        <v>664950</v>
       </c>
       <c r="R7" t="n">
-        <v>6558798</v>
+        <v>6558784</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,10 +1405,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122310052</v>
+        <v>122309088</v>
       </c>
       <c r="B8" t="n">
-        <v>91397</v>
+        <v>79263</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,25 +1417,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6031</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>664950</v>
+        <v>664875</v>
       </c>
       <c r="R8" t="n">
-        <v>6558784</v>
+        <v>6558798</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 28-2025 artfynd.xlsx
+++ b/artfynd/A 28-2025 artfynd.xlsx
@@ -1296,7 +1296,7 @@
         <v>122310052</v>
       </c>
       <c r="B7" t="n">
-        <v>91397</v>
+        <v>91407</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1405,10 +1405,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122309088</v>
+        <v>122308739</v>
       </c>
       <c r="B8" t="n">
-        <v>79263</v>
+        <v>90809</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1421,21 +1421,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1445,13 +1445,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>664875</v>
+        <v>664874</v>
       </c>
       <c r="R8" t="n">
-        <v>6558798</v>
+        <v>6558753</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1505,22 +1505,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122308739</v>
+        <v>122309088</v>
       </c>
       <c r="B9" t="n">
-        <v>90799</v>
+        <v>79264</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1533,21 +1533,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1557,13 +1557,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>664874</v>
+        <v>664875</v>
       </c>
       <c r="R9" t="n">
-        <v>6558753</v>
+        <v>6558798</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,12 +1617,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Pia Rydh</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Pia Rydh</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 28-2025 artfynd.xlsx
+++ b/artfynd/A 28-2025 artfynd.xlsx
@@ -1052,7 +1052,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122064436</v>
+        <v>122050719</v>
       </c>
       <c r="B5" t="n">
         <v>57390</v>
@@ -1085,32 +1085,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Råby, Råby, Srm</t>
+          <t>Botkyrka kommun, Botkyrka kommun, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>664974</v>
+        <v>664977</v>
       </c>
       <c r="R5" t="n">
-        <v>6558875</v>
+        <v>6558864</v>
       </c>
       <c r="S5" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1164,19 +1157,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122050719</v>
+        <v>122064436</v>
       </c>
       <c r="B6" t="n">
         <v>57390</v>
@@ -1209,25 +1202,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Botkyrka kommun, Botkyrka kommun, Srm</t>
+          <t>Råby, Råby, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>664977</v>
+        <v>664974</v>
       </c>
       <c r="R6" t="n">
-        <v>6558864</v>
+        <v>6558875</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1281,12 +1281,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122308739</v>
+        <v>122308728</v>
       </c>
       <c r="B8" t="n">
-        <v>90809</v>
+        <v>5173</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,25 +1417,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1445,13 +1445,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>664874</v>
+        <v>664880</v>
       </c>
       <c r="R8" t="n">
-        <v>6558753</v>
+        <v>6558758</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1505,22 +1505,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Pia Rydh</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Pia Rydh</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122309088</v>
+        <v>122308739</v>
       </c>
       <c r="B9" t="n">
-        <v>79264</v>
+        <v>90809</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1533,21 +1533,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1557,13 +1557,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>664875</v>
+        <v>664874</v>
       </c>
       <c r="R9" t="n">
-        <v>6558798</v>
+        <v>6558753</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,22 +1617,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122308728</v>
+        <v>122309088</v>
       </c>
       <c r="B10" t="n">
-        <v>5173</v>
+        <v>79264</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>664880</v>
+        <v>664875</v>
       </c>
       <c r="R10" t="n">
-        <v>6558758</v>
+        <v>6558798</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 28-2025 artfynd.xlsx
+++ b/artfynd/A 28-2025 artfynd.xlsx
@@ -1055,7 +1055,7 @@
         <v>122050719</v>
       </c>
       <c r="B5" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>122064436</v>
       </c>
       <c r="B6" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1293,10 +1293,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122310052</v>
+        <v>122308728</v>
       </c>
       <c r="B7" t="n">
-        <v>91407</v>
+        <v>5173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1309,21 +1309,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6031</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1333,10 +1333,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>664950</v>
+        <v>664880</v>
       </c>
       <c r="R7" t="n">
-        <v>6558784</v>
+        <v>6558758</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,10 +1405,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122308728</v>
+        <v>122310052</v>
       </c>
       <c r="B8" t="n">
-        <v>5173</v>
+        <v>91419</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1421,21 +1421,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>6031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>664880</v>
+        <v>664950</v>
       </c>
       <c r="R8" t="n">
-        <v>6558758</v>
+        <v>6558784</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,10 +1517,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122308739</v>
+        <v>122309088</v>
       </c>
       <c r="B9" t="n">
-        <v>90809</v>
+        <v>79269</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1533,21 +1533,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1557,13 +1557,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>664874</v>
+        <v>664875</v>
       </c>
       <c r="R9" t="n">
-        <v>6558753</v>
+        <v>6558798</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,22 +1617,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Pia Rydh</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Pia Rydh</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122309088</v>
+        <v>122308739</v>
       </c>
       <c r="B10" t="n">
-        <v>79264</v>
+        <v>90821</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1669,13 +1669,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>664875</v>
+        <v>664874</v>
       </c>
       <c r="R10" t="n">
-        <v>6558798</v>
+        <v>6558753</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,12 +1729,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 28-2025 artfynd.xlsx
+++ b/artfynd/A 28-2025 artfynd.xlsx
@@ -1052,7 +1052,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122050719</v>
+        <v>122064436</v>
       </c>
       <c r="B5" t="n">
         <v>57395</v>
@@ -1085,25 +1085,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Botkyrka kommun, Botkyrka kommun, Srm</t>
+          <t>Råby, Råby, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>664977</v>
+        <v>664974</v>
       </c>
       <c r="R5" t="n">
-        <v>6558864</v>
+        <v>6558875</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1157,19 +1164,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122064436</v>
+        <v>122050719</v>
       </c>
       <c r="B6" t="n">
         <v>57395</v>
@@ -1202,32 +1209,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Råby, Råby, Srm</t>
+          <t>Botkyrka kommun, Botkyrka kommun, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>664974</v>
+        <v>664977</v>
       </c>
       <c r="R6" t="n">
-        <v>6558875</v>
+        <v>6558864</v>
       </c>
       <c r="S6" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1281,22 +1281,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122308728</v>
+        <v>122309088</v>
       </c>
       <c r="B7" t="n">
-        <v>5173</v>
+        <v>79269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1305,25 +1305,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1333,10 +1333,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>664880</v>
+        <v>664875</v>
       </c>
       <c r="R7" t="n">
-        <v>6558758</v>
+        <v>6558798</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1408,7 +1408,7 @@
         <v>122310052</v>
       </c>
       <c r="B8" t="n">
-        <v>91419</v>
+        <v>91424</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1517,10 +1517,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122309088</v>
+        <v>122308728</v>
       </c>
       <c r="B9" t="n">
-        <v>79269</v>
+        <v>5173</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,25 +1529,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>664875</v>
+        <v>664880</v>
       </c>
       <c r="R9" t="n">
-        <v>6558798</v>
+        <v>6558758</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1632,7 +1632,7 @@
         <v>122308739</v>
       </c>
       <c r="B10" t="n">
-        <v>90821</v>
+        <v>90828</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 28-2025 artfynd.xlsx
+++ b/artfynd/A 28-2025 artfynd.xlsx
@@ -1052,7 +1052,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122064436</v>
+        <v>122050719</v>
       </c>
       <c r="B5" t="n">
         <v>57395</v>
@@ -1070,11 +1070,6 @@
       <c r="E5" t="n">
         <v>100049</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -1085,32 +1080,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Råby, Råby, Srm</t>
+          <t>Botkyrka kommun, Botkyrka kommun, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>664974</v>
+        <v>664977</v>
       </c>
       <c r="R5" t="n">
-        <v>6558875</v>
+        <v>6558864</v>
       </c>
       <c r="S5" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1164,19 +1152,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122050719</v>
+        <v>122064436</v>
       </c>
       <c r="B6" t="n">
         <v>57395</v>
@@ -1194,11 +1182,6 @@
       <c r="E6" t="n">
         <v>100049</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -1209,25 +1192,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Botkyrka kommun, Botkyrka kommun, Srm</t>
+          <t>Råby, Råby, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>664977</v>
+        <v>664974</v>
       </c>
       <c r="R6" t="n">
-        <v>6558864</v>
+        <v>6558875</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1281,22 +1271,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122309088</v>
+        <v>122310052</v>
       </c>
       <c r="B7" t="n">
-        <v>79269</v>
+        <v>91429</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1305,25 +1295,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
+        <v>6031</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1333,10 +1318,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>664875</v>
+        <v>664950</v>
       </c>
       <c r="R7" t="n">
-        <v>6558798</v>
+        <v>6558784</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,7 +1353,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1378,7 +1363,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,10 +1390,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122310052</v>
+        <v>122308728</v>
       </c>
       <c r="B8" t="n">
-        <v>91424</v>
+        <v>5173</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1421,21 +1406,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6031</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Blomkålssvamp</t>
-        </is>
+        <v>100526</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1445,10 +1425,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>664950</v>
+        <v>664880</v>
       </c>
       <c r="R8" t="n">
-        <v>6558784</v>
+        <v>6558758</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1490,7 +1470,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,10 +1497,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122308728</v>
+        <v>122308739</v>
       </c>
       <c r="B9" t="n">
-        <v>5173</v>
+        <v>90833</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,25 +1509,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
+        <v>5442</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1557,13 +1532,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>664880</v>
+        <v>664874</v>
       </c>
       <c r="R9" t="n">
-        <v>6558758</v>
+        <v>6558753</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1592,7 +1567,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1577,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,22 +1592,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122308739</v>
+        <v>122309088</v>
       </c>
       <c r="B10" t="n">
-        <v>90828</v>
+        <v>79270</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1645,21 +1620,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
+        <v>6453</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1669,13 +1639,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>664874</v>
+        <v>664875</v>
       </c>
       <c r="R10" t="n">
-        <v>6558753</v>
+        <v>6558798</v>
       </c>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1704,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1684,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,12 +1699,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Pia Rydh</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Pia Rydh</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 28-2025 artfynd.xlsx
+++ b/artfynd/A 28-2025 artfynd.xlsx
@@ -1283,10 +1283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122310052</v>
+        <v>122308739</v>
       </c>
       <c r="B7" t="n">
-        <v>91429</v>
+        <v>90846</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,20 +1295,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6031</v>
+        <v>5442</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1318,13 +1323,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>664950</v>
+        <v>664874</v>
       </c>
       <c r="R7" t="n">
-        <v>6558784</v>
+        <v>6558753</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1353,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1363,7 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,22 +1383,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122308728</v>
+        <v>122310052</v>
       </c>
       <c r="B8" t="n">
-        <v>5173</v>
+        <v>91442</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1406,16 +1411,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>6031</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1425,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>664880</v>
+        <v>664950</v>
       </c>
       <c r="R8" t="n">
-        <v>6558758</v>
+        <v>6558784</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1470,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,7 +1480,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,10 +1507,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122308739</v>
+        <v>122308728</v>
       </c>
       <c r="B9" t="n">
-        <v>90833</v>
+        <v>5173</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1509,20 +1519,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>100526</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1532,13 +1547,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>664874</v>
+        <v>664880</v>
       </c>
       <c r="R9" t="n">
-        <v>6558753</v>
+        <v>6558758</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1567,7 +1582,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1577,7 +1592,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,12 +1607,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Pia Rydh</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Pia Rydh</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1607,7 +1622,7 @@
         <v>122309088</v>
       </c>
       <c r="B10" t="n">
-        <v>79270</v>
+        <v>79274</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1621,6 +1636,11 @@
       </c>
       <c r="E10" t="n">
         <v>6453</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>

--- a/artfynd/A 28-2025 artfynd.xlsx
+++ b/artfynd/A 28-2025 artfynd.xlsx
@@ -1283,10 +1283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122308739</v>
+        <v>122310052</v>
       </c>
       <c r="B7" t="n">
-        <v>90846</v>
+        <v>91455</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,25 +1295,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>664874</v>
+        <v>664950</v>
       </c>
       <c r="R7" t="n">
-        <v>6558753</v>
+        <v>6558784</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,22 +1383,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Pia Rydh</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Pia Rydh</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122310052</v>
+        <v>122308739</v>
       </c>
       <c r="B8" t="n">
-        <v>91442</v>
+        <v>90859</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,25 +1407,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6031</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1435,13 +1435,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>664950</v>
+        <v>664874</v>
       </c>
       <c r="R8" t="n">
-        <v>6558784</v>
+        <v>6558753</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,12 +1495,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 28-2025 artfynd.xlsx
+++ b/artfynd/A 28-2025 artfynd.xlsx
@@ -1283,10 +1283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122310052</v>
+        <v>122309088</v>
       </c>
       <c r="B7" t="n">
-        <v>91455</v>
+        <v>79274</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,25 +1295,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6031</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>664950</v>
+        <v>664875</v>
       </c>
       <c r="R7" t="n">
-        <v>6558784</v>
+        <v>6558798</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1619,10 +1619,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122309088</v>
+        <v>122310052</v>
       </c>
       <c r="B10" t="n">
-        <v>79274</v>
+        <v>91455</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,25 +1631,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1659,10 +1659,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>664875</v>
+        <v>664950</v>
       </c>
       <c r="R10" t="n">
-        <v>6558798</v>
+        <v>6558784</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 28-2025 artfynd.xlsx
+++ b/artfynd/A 28-2025 artfynd.xlsx
@@ -1398,7 +1398,7 @@
         <v>122308739</v>
       </c>
       <c r="B8" t="n">
-        <v>90859</v>
+        <v>90853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>122310052</v>
       </c>
       <c r="B10" t="n">
-        <v>91455</v>
+        <v>91456</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 28-2025 artfynd.xlsx
+++ b/artfynd/A 28-2025 artfynd.xlsx
@@ -1283,10 +1283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122309088</v>
+        <v>122308739</v>
       </c>
       <c r="B7" t="n">
-        <v>79274</v>
+        <v>90853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1299,21 +1299,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>664875</v>
+        <v>664874</v>
       </c>
       <c r="R7" t="n">
-        <v>6558798</v>
+        <v>6558753</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,22 +1383,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122308739</v>
+        <v>122309088</v>
       </c>
       <c r="B8" t="n">
-        <v>90853</v>
+        <v>79274</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,21 +1411,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1435,13 +1435,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>664874</v>
+        <v>664875</v>
       </c>
       <c r="R8" t="n">
-        <v>6558753</v>
+        <v>6558798</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,22 +1495,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Pia Rydh</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Pia Rydh</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122308728</v>
+        <v>122310052</v>
       </c>
       <c r="B9" t="n">
-        <v>5173</v>
+        <v>91456</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1523,21 +1523,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>6031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>664880</v>
+        <v>664950</v>
       </c>
       <c r="R9" t="n">
-        <v>6558758</v>
+        <v>6558784</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,10 +1619,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122310052</v>
+        <v>122308728</v>
       </c>
       <c r="B10" t="n">
-        <v>91456</v>
+        <v>5173</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,21 +1635,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6031</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1659,10 +1659,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>664950</v>
+        <v>664880</v>
       </c>
       <c r="R10" t="n">
-        <v>6558784</v>
+        <v>6558758</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 28-2025 artfynd.xlsx
+++ b/artfynd/A 28-2025 artfynd.xlsx
@@ -1283,10 +1283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122308739</v>
+        <v>122310052</v>
       </c>
       <c r="B7" t="n">
-        <v>90853</v>
+        <v>91457</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,25 +1295,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>664874</v>
+        <v>664950</v>
       </c>
       <c r="R7" t="n">
-        <v>6558753</v>
+        <v>6558784</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,22 +1383,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Pia Rydh</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Pia Rydh</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122309088</v>
+        <v>122308728</v>
       </c>
       <c r="B8" t="n">
-        <v>79274</v>
+        <v>5173</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,25 +1407,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>664875</v>
+        <v>664880</v>
       </c>
       <c r="R8" t="n">
-        <v>6558798</v>
+        <v>6558758</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,10 +1507,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122310052</v>
+        <v>122309088</v>
       </c>
       <c r="B9" t="n">
-        <v>91456</v>
+        <v>79275</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1519,25 +1519,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6031</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>664950</v>
+        <v>664875</v>
       </c>
       <c r="R9" t="n">
-        <v>6558784</v>
+        <v>6558798</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,10 +1619,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122308728</v>
+        <v>122308739</v>
       </c>
       <c r="B10" t="n">
-        <v>5173</v>
+        <v>90854</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,25 +1631,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>664880</v>
+        <v>664874</v>
       </c>
       <c r="R10" t="n">
-        <v>6558758</v>
+        <v>6558753</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,12 +1719,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 28-2025 artfynd.xlsx
+++ b/artfynd/A 28-2025 artfynd.xlsx
@@ -1283,10 +1283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122310052</v>
+        <v>122308728</v>
       </c>
       <c r="B7" t="n">
-        <v>91457</v>
+        <v>5173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1299,21 +1299,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6031</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>664950</v>
+        <v>664880</v>
       </c>
       <c r="R7" t="n">
-        <v>6558784</v>
+        <v>6558758</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122308728</v>
+        <v>122309088</v>
       </c>
       <c r="B8" t="n">
-        <v>5173</v>
+        <v>79278</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,25 +1407,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>664880</v>
+        <v>664875</v>
       </c>
       <c r="R8" t="n">
-        <v>6558758</v>
+        <v>6558798</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,10 +1507,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122309088</v>
+        <v>122308739</v>
       </c>
       <c r="B9" t="n">
-        <v>79275</v>
+        <v>90857</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1523,21 +1523,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>664875</v>
+        <v>664874</v>
       </c>
       <c r="R9" t="n">
-        <v>6558798</v>
+        <v>6558753</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,22 +1607,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122308739</v>
+        <v>122310052</v>
       </c>
       <c r="B10" t="n">
-        <v>90854</v>
+        <v>91460</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,25 +1631,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>6031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>664874</v>
+        <v>664950</v>
       </c>
       <c r="R10" t="n">
-        <v>6558753</v>
+        <v>6558784</v>
       </c>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,12 +1719,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Pia Rydh</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Pia Rydh</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
